--- a/data/trans_orig/P43-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P43-Habitat-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,25 +526,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2007</t>
+          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2007 (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +548,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -564,17 +557,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -645,41 +627,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -702,13 +649,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -723,37 +663,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>253</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>243732</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220153</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267431</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>219435</t>
+          <t>220153</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>268582</t>
+          <t>267431</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>243732</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>219435</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>268582</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>35,67%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>32,12%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>39,31%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -836,37 +741,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>438</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>439536</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>415837</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>463115</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>414686</t>
+          <t>415837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>463833</t>
+          <t>463115</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>439536</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>414686</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>463833</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>64,33%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>60,69%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>67,88%</t>
+          <t>67,78%</t>
         </is>
       </c>
     </row>
@@ -949,37 +819,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>691</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>683268</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>683268</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>683268</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1013,41 +883,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>683268</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>683268</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>683268</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1066,37 +901,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>341470</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>312402</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>372069</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313519</t>
+          <t>312402</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>371510</t>
+          <t>372069</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,47 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>341470</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>313519</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>371510</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>35,38%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>32,48%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>38,49%</t>
+          <t>38,55%</t>
         </is>
       </c>
     </row>
@@ -1179,37 +979,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>583</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>623739</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>593140</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>652807</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>593699</t>
+          <t>593140</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>651690</t>
+          <t>652807</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,47 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>623739</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>593699</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>651690</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>64,62%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>61,51%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>67,52%</t>
+          <t>67,63%</t>
         </is>
       </c>
     </row>
@@ -1292,37 +1057,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>905</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>965209</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>965209</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>965209</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1356,41 +1121,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>905</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>965209</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>965209</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>965209</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1409,37 +1139,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>267</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>264087</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>238113</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>288046</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>239294</t>
+          <t>238113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>288365</t>
+          <t>288046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,47 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>264087</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>239294</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>288365</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>38,93%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>35,27%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>42,51%</t>
+          <t>42,46%</t>
         </is>
       </c>
     </row>
@@ -1522,37 +1217,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>423</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>414325</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>390366</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>440299</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>390047</t>
+          <t>390366</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>439118</t>
+          <t>440299</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,47 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>423</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>414325</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>390047</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>439118</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>61,07%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>57,49%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>64,73%</t>
+          <t>64,9%</t>
         </is>
       </c>
     </row>
@@ -1635,37 +1295,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>690</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>678412</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>678412</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>678412</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1699,41 +1359,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>678412</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>678412</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>678412</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1752,37 +1377,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>410</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>424152</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>392467</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>458707</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>388097</t>
+          <t>392467</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>454226</t>
+          <t>458707</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>424152</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>388097</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>454226</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>41,08%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>37,58%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>43,99%</t>
+          <t>44,42%</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1455,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>581</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>608453</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>573898</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>640138</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>578379</t>
+          <t>573898</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>644508</t>
+          <t>640138</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>608453</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>578379</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>644508</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>58,92%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>56,01%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>62,42%</t>
+          <t>61,99%</t>
         </is>
       </c>
     </row>
@@ -1978,37 +1533,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>991</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1032605</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1032605</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1032605</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2042,41 +1597,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>991</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1032605</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1032605</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1032605</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2095,37 +1615,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1273441</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1217806</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1326804</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1215683</t>
+          <t>1217806</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1329323</t>
+          <t>1326804</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,47 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1273441</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1215683</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1329323</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>37,91%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>36,19%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>39,57%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -2208,37 +1693,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2086053</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2032690</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2141688</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2030171</t>
+          <t>2032690</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2143811</t>
+          <t>2141688</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,47 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>2086053</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>2030171</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>2143811</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>62,09%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>60,43%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>63,81%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -2321,37 +1771,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3359494</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3359494</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3359494</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2385,41 +1835,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3277</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3359494</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>3359494</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3359494</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2433,14 +1848,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -2454,7 +1868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2473,25 +1887,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2012</t>
+          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2012 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +1909,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2511,17 +1918,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2592,41 +1988,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -2649,13 +2010,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2670,37 +2024,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>328239</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>302072</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352877</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2069,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>300684</t>
+          <t>302072</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>357236</t>
+          <t>352877</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,47 +2084,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>328239</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>300684</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>357236</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>47,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>43,38%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>51,54%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -2783,37 +2102,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>343</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>364848</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>340210</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>391015</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2147,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>335851</t>
+          <t>340210</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>392403</t>
+          <t>391015</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,47 +2162,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>364848</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>335851</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>392403</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>52,64%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>48,46%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>56,62%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -2896,37 +2180,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>646</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>693087</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>693087</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>693087</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2960,41 +2244,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>693087</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>693087</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>693087</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3013,37 +2262,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>419</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>463929</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>431079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>499619</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +2307,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>427860</t>
+          <t>431079</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>495981</t>
+          <t>499619</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,47 +2322,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>463929</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>427860</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>495981</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>45,27%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>41,75%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>48,39%</t>
+          <t>48,75%</t>
         </is>
       </c>
     </row>
@@ -3126,37 +2340,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>514</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>560968</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>525278</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>593818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +2385,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>528916</t>
+          <t>525278</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>597037</t>
+          <t>593818</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,47 +2400,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>560968</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>528916</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>597037</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>54,73%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>51,61%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>58,25%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -3239,37 +2418,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>933</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1024897</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1024897</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1024897</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3303,41 +2482,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>933</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1024897</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1024897</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1024897</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3356,37 +2500,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>328</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370652</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>342238</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>398867</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +2545,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>339486</t>
+          <t>342238</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>397702</t>
+          <t>398867</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,47 +2560,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>370652</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>339486</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>397702</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>47,89%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>43,87%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>51,39%</t>
+          <t>51,54%</t>
         </is>
       </c>
     </row>
@@ -3469,37 +2578,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>374</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>403246</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>375031</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>431660</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +2623,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>376196</t>
+          <t>375031</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>434412</t>
+          <t>431660</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,47 +2638,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>403246</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>376196</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>434412</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>52,11%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>48,61%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>56,13%</t>
+          <t>55,78%</t>
         </is>
       </c>
     </row>
@@ -3582,37 +2656,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>702</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>773898</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>773898</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>773898</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3646,41 +2720,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>773898</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>773898</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>773898</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3699,37 +2738,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>473</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>504428</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>473042</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>540009</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +2783,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>469710</t>
+          <t>473042</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>538597</t>
+          <t>540009</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,47 +2798,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>504428</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>469710</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>538597</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>48,29%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>44,96%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>51,56%</t>
+          <t>51,69%</t>
         </is>
       </c>
     </row>
@@ -3812,37 +2816,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>523</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>540248</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>504667</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>571634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +2861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>506079</t>
+          <t>504667</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>574966</t>
+          <t>571634</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,47 +2876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>540248</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>506079</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>574966</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>51,71%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>48,44%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>55,04%</t>
+          <t>54,72%</t>
         </is>
       </c>
     </row>
@@ -3925,37 +2894,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>996</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1044676</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1044676</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1044676</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3989,41 +2958,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>996</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1044676</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1044676</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1044676</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4042,37 +2976,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1667249</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1607282</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1727835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +3021,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1606844</t>
+          <t>1607282</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1729955</t>
+          <t>1727835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,47 +3036,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1667249</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1606844</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1729955</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>47,14%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>45,44%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>48,92%</t>
+          <t>48,86%</t>
         </is>
       </c>
     </row>
@@ -4155,37 +3054,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1869309</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1808723</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1929276</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +3099,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1806603</t>
+          <t>1808723</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1929714</t>
+          <t>1929276</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,47 +3114,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1754</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1869309</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1806603</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1929714</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>52,86%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>51,08%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>54,56%</t>
+          <t>54,55%</t>
         </is>
       </c>
     </row>
@@ -4268,37 +3132,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3536558</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3536558</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3536558</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4332,41 +3196,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3277</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3536558</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>3536558</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3536558</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4380,14 +3209,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -4401,7 +3229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4420,25 +3248,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2016</t>
+          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2016 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +3270,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4458,17 +3279,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -4539,41 +3349,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -4596,13 +3371,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -4617,37 +3385,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>319</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>334215</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>308018</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>360149</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +3430,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>308290</t>
+          <t>308018</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>360430</t>
+          <t>360149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,47 +3445,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>334215</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>308290</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>360430</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>50,01%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>46,13%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>53,93%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -4730,37 +3463,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>343</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>334113</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>308179</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>360310</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +3508,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307898</t>
+          <t>308179</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>360038</t>
+          <t>360310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,47 +3523,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>334113</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>307898</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>360038</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>49,99%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>46,07%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>53,87%</t>
+          <t>53,91%</t>
         </is>
       </c>
     </row>
@@ -4843,37 +3541,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>662</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>668328</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>668328</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>668328</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4907,41 +3605,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>668328</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>668328</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>668328</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4960,37 +3623,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>493</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>543552</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>511813</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>578184</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +3668,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>510249</t>
+          <t>511813</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>576120</t>
+          <t>578184</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,47 +3683,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>543552</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>510249</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>576120</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>52,55%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>49,33%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>55,7%</t>
+          <t>55,9%</t>
         </is>
       </c>
     </row>
@@ -5073,37 +3701,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>476</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>490717</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>456085</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>522456</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +3746,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>458149</t>
+          <t>456085</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>524020</t>
+          <t>522456</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,47 +3761,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>490717</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>458149</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>524020</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>47,45%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>44,3%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>50,67%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -5186,37 +3779,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>969</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1034269</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1034269</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1034269</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5250,41 +3843,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1034269</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1034269</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1034269</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5303,37 +3861,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>309</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>342091</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>312713</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>371635</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +3906,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>314821</t>
+          <t>312713</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>371821</t>
+          <t>371635</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,47 +3921,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>342091</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>314821</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>371821</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>43,76%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>40,27%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>47,57%</t>
+          <t>47,54%</t>
         </is>
       </c>
     </row>
@@ -5416,37 +3939,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>424</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>439617</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>410073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>468995</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +3984,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>409887</t>
+          <t>410073</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>466887</t>
+          <t>468995</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,47 +3999,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>439617</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>409887</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>466887</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>56,24%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>52,43%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>59,73%</t>
+          <t>60,0%</t>
         </is>
       </c>
     </row>
@@ -5529,37 +4017,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>733</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>781708</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>781708</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>781708</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5593,41 +4081,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>733</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>781708</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>781708</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>781708</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5646,37 +4099,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>474</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>537442</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>503752</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>569585</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +4144,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>506169</t>
+          <t>503752</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>573548</t>
+          <t>569585</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,47 +4159,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>537442</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>506169</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>573548</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>51,91%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>48,89%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>55,39%</t>
+          <t>55,01%</t>
         </is>
       </c>
     </row>
@@ -5759,37 +4177,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>477</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>497943</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>465800</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>531633</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +4222,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>461837</t>
+          <t>465800</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>529216</t>
+          <t>531633</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,47 +4237,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>497943</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>461837</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>529216</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>48,09%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>44,61%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>51,11%</t>
+          <t>51,35%</t>
         </is>
       </c>
     </row>
@@ -5872,37 +4255,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>951</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1035385</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1035385</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1035385</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5936,41 +4319,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1035385</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1035385</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1035385</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5989,37 +4337,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1757300</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1698387</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1824187</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +4382,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1694936</t>
+          <t>1698387</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1816789</t>
+          <t>1824187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,47 +4397,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1595</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1757300</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1694936</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1816789</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>49,93%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>48,16%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>51,62%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -6102,37 +4415,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1762390</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1695503</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1821303</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +4460,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1702901</t>
+          <t>1695503</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1824754</t>
+          <t>1821303</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,47 +4475,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1720</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1762390</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1702901</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1824754</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>50,07%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>48,38%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>51,84%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -6215,37 +4493,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3519690</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3519690</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3519690</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6279,41 +4557,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3315</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3519690</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>3519690</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3519690</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6327,14 +4570,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -6348,7 +4590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6367,25 +4609,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2023</t>
+          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2023 (tasa de respuesta: 99,26%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +4631,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6405,17 +4640,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -6486,41 +4710,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -6543,13 +4732,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -6564,37 +4746,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>587</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>271231</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>252976</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>290441</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +4791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>252322</t>
+          <t>252976</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>288988</t>
+          <t>290441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,47 +4806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>271231</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>252322</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>288988</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>53,13%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>49,43%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>56,61%</t>
+          <t>56,9%</t>
         </is>
       </c>
     </row>
@@ -6677,37 +4824,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>358</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>239235</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220025</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>257490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +4869,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>221478</t>
+          <t>220025</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258144</t>
+          <t>257490</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,47 +4884,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>239235</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>221478</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>258144</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>46,87%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>43,39%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>50,57%</t>
+          <t>50,44%</t>
         </is>
       </c>
     </row>
@@ -6790,37 +4902,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>945</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>510466</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>510466</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>510466</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6854,41 +4966,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>510466</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>510466</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>510466</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6907,37 +4984,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>677</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>362303</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339361</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>385103</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +5029,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>337959</t>
+          <t>339361</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>384849</t>
+          <t>385103</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,47 +5044,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>362303</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>337959</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>384849</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>49,33%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>46,02%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>52,4%</t>
+          <t>52,44%</t>
         </is>
       </c>
     </row>
@@ -7020,37 +5062,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>498</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>372090</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>349290</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>395032</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>349544</t>
+          <t>349290</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>396434</t>
+          <t>395032</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,47 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>498</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>372090</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>349544</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>396434</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>50,67%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>47,6%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>53,98%</t>
+          <t>53,79%</t>
         </is>
       </c>
     </row>
@@ -7133,37 +5140,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>734393</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>734393</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>734393</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7197,41 +5204,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1175</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>734393</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>734393</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>734393</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7250,37 +5222,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>438</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>505167</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>399490</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>624443</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +5267,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>401392</t>
+          <t>399490</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>627973</t>
+          <t>624443</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,47 +5282,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>505167</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>401392</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>627973</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>69,25%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>55,02%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>86,08%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -7363,37 +5300,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>295</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>224318</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>105042</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>329995</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +5345,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101512</t>
+          <t>105042</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328093</t>
+          <t>329995</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,47 +5360,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>224318</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>101512</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>328093</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>30,75%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>44,98%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -7476,37 +5378,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>733</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>729485</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>729485</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>729485</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7540,41 +5442,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>733</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>729485</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>729485</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>729485</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7593,37 +5460,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>765</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>444437</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>332508</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>493374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +5505,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>339638</t>
+          <t>332508</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>494826</t>
+          <t>493374</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,47 +5520,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>444437</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>339638</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>494826</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>51,88%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>39,65%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>57,77%</t>
+          <t>57,6%</t>
         </is>
       </c>
     </row>
@@ -7706,37 +5538,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>412</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>412175</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>363238</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>524104</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +5583,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>361786</t>
+          <t>363238</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>516974</t>
+          <t>524104</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,47 +5598,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>412175</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>361786</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>516974</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>48,12%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>42,23%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>60,35%</t>
+          <t>61,18%</t>
         </is>
       </c>
     </row>
@@ -7819,37 +5616,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>856612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>856612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>856612</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7883,41 +5680,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1177</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>856612</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>856612</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>856612</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7936,37 +5698,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1583137</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1445705</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1873457</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +5743,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1454515</t>
+          <t>1445705</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1883137</t>
+          <t>1873457</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,47 +5758,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1583137</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1454515</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1883137</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>55,92%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>51,38%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>66,52%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -8049,37 +5776,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1563</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1247819</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>957499</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1385251</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +5821,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>947819</t>
+          <t>957499</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1376441</t>
+          <t>1385251</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,47 +5836,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1563</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1247819</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>947819</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1376441</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>44,08%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>33,48%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>48,62%</t>
+          <t>48,93%</t>
         </is>
       </c>
     </row>
@@ -8162,37 +5854,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2830956</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2830956</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2830956</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8226,41 +5918,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>4030</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>2830956</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>2830956</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>2830956</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8274,14 +5931,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_orig/P43-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P43-Habitat-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>220153</t>
+          <t>220686</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>267431</t>
+          <t>268739</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>220153</t>
+          <t>220686</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>267431</t>
+          <t>268739</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>415837</t>
+          <t>414529</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>463115</t>
+          <t>462582</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>415837</t>
+          <t>414529</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>463115</t>
+          <t>462582</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,7%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>312402</t>
+          <t>311395</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>372069</t>
+          <t>371637</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>312402</t>
+          <t>311395</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>372069</t>
+          <t>371637</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>593140</t>
+          <t>593572</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>652807</t>
+          <t>653814</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>593140</t>
+          <t>593572</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>652807</t>
+          <t>653814</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,74%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>238113</t>
+          <t>240326</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>288046</t>
+          <t>292663</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>238113</t>
+          <t>240326</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>288046</t>
+          <t>292663</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>43,14%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>390366</t>
+          <t>385749</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>440299</t>
+          <t>438086</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>390366</t>
+          <t>385749</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>440299</t>
+          <t>438086</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,58%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>392467</t>
+          <t>389851</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>458707</t>
+          <t>458227</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>392467</t>
+          <t>389851</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>458707</t>
+          <t>458227</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,38%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>573898</t>
+          <t>574378</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>640138</t>
+          <t>642754</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>573898</t>
+          <t>574378</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>640138</t>
+          <t>642754</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,25%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1217806</t>
+          <t>1214792</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1326804</t>
+          <t>1330182</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1217806</t>
+          <t>1214792</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1326804</t>
+          <t>1330182</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2032690</t>
+          <t>2029312</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2141688</t>
+          <t>2144702</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2032690</t>
+          <t>2029312</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2141688</t>
+          <t>2144702</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,84%</t>
         </is>
       </c>
     </row>
@@ -2034,12 +2034,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>302072</t>
+          <t>300206</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>352877</t>
+          <t>354094</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>302072</t>
+          <t>300206</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>352877</t>
+          <t>354094</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,09%</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>340210</t>
+          <t>338993</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>391015</t>
+          <t>392881</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>340210</t>
+          <t>338993</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>391015</t>
+          <t>392881</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -2272,12 +2272,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>431079</t>
+          <t>429522</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>499619</t>
+          <t>494698</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>431079</t>
+          <t>429522</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>499619</t>
+          <t>494698</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,27%</t>
         </is>
       </c>
     </row>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>525278</t>
+          <t>530199</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>593818</t>
+          <t>595375</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>525278</t>
+          <t>530199</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>593818</t>
+          <t>595375</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>342238</t>
+          <t>341367</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>398867</t>
+          <t>396911</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>342238</t>
+          <t>341367</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>398867</t>
+          <t>396911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,29%</t>
         </is>
       </c>
     </row>
@@ -2588,12 +2588,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>375031</t>
+          <t>376987</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>431660</t>
+          <t>432531</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>375031</t>
+          <t>376987</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>431660</t>
+          <t>432531</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -2748,12 +2748,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>473042</t>
+          <t>474392</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>540009</t>
+          <t>536832</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>473042</t>
+          <t>474392</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>540009</t>
+          <t>536832</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,39%</t>
         </is>
       </c>
     </row>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>504667</t>
+          <t>507844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>571634</t>
+          <t>570284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>504667</t>
+          <t>507844</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>571634</t>
+          <t>570284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,59%</t>
         </is>
       </c>
     </row>
@@ -2986,12 +2986,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1607282</t>
+          <t>1611161</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1727835</t>
+          <t>1727789</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1607282</t>
+          <t>1611161</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1727835</t>
+          <t>1727789</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1808723</t>
+          <t>1808769</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1929276</t>
+          <t>1925397</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1808723</t>
+          <t>1808769</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1929276</t>
+          <t>1925397</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,44%</t>
         </is>
       </c>
     </row>
@@ -3395,12 +3395,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>308018</t>
+          <t>310020</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>360149</t>
+          <t>364113</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>308018</t>
+          <t>310020</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>360149</t>
+          <t>364113</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,48%</t>
         </is>
       </c>
     </row>
@@ -3473,12 +3473,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>308179</t>
+          <t>304215</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>360310</t>
+          <t>358308</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308179</t>
+          <t>304215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>360310</t>
+          <t>358308</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,61%</t>
         </is>
       </c>
     </row>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>511813</t>
+          <t>512284</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>578184</t>
+          <t>575802</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>511813</t>
+          <t>512284</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>578184</t>
+          <t>575802</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,67%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>456085</t>
+          <t>458467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>522456</t>
+          <t>521985</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>456085</t>
+          <t>458467</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>522456</t>
+          <t>521985</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -3871,12 +3871,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>312713</t>
+          <t>314923</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>371635</t>
+          <t>372594</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>312713</t>
+          <t>314923</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>371635</t>
+          <t>372594</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -3949,12 +3949,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>410073</t>
+          <t>409114</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>468995</t>
+          <t>466785</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>410073</t>
+          <t>409114</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>468995</t>
+          <t>466785</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>503752</t>
+          <t>505782</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>569585</t>
+          <t>573453</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>503752</t>
+          <t>505782</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>569585</t>
+          <t>573453</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,39%</t>
         </is>
       </c>
     </row>
@@ -4187,12 +4187,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>465800</t>
+          <t>461932</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>531633</t>
+          <t>529603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>465800</t>
+          <t>461932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>531633</t>
+          <t>529603</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,15%</t>
         </is>
       </c>
     </row>
@@ -4347,12 +4347,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1698387</t>
+          <t>1697844</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1824187</t>
+          <t>1820096</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1698387</t>
+          <t>1697844</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1824187</t>
+          <t>1820096</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,71%</t>
         </is>
       </c>
     </row>
@@ -4425,12 +4425,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1695503</t>
+          <t>1699594</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1821303</t>
+          <t>1821846</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1695503</t>
+          <t>1699594</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1821303</t>
+          <t>1821846</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4475,12 +4475,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,76%</t>
         </is>
       </c>
     </row>
@@ -4751,32 +4751,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>271231</t>
+          <t>289241</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>252976</t>
+          <t>269127</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>290441</t>
+          <t>309991</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4786,32 +4786,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>271231</t>
+          <t>289241</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>252976</t>
+          <t>269127</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>290441</t>
+          <t>309991</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,06%</t>
         </is>
       </c>
     </row>
@@ -4829,32 +4829,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>239235</t>
+          <t>263718</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>220025</t>
+          <t>242968</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>257490</t>
+          <t>283832</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4864,32 +4864,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>239235</t>
+          <t>263718</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220025</t>
+          <t>242968</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257490</t>
+          <t>283832</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>51,33%</t>
         </is>
       </c>
     </row>
@@ -4907,17 +4907,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>510466</t>
+          <t>552959</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>510466</t>
+          <t>552959</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>510466</t>
+          <t>552959</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4942,17 +4942,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>510466</t>
+          <t>552959</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>510466</t>
+          <t>552959</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>510466</t>
+          <t>552959</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4989,32 +4989,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>362303</t>
+          <t>401238</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>339361</t>
+          <t>375294</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>385103</t>
+          <t>425018</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5024,32 +5024,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>362303</t>
+          <t>401238</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>339361</t>
+          <t>375294</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>385103</t>
+          <t>425018</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>51,85%</t>
         </is>
       </c>
     </row>
@@ -5067,32 +5067,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>372090</t>
+          <t>418450</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>349290</t>
+          <t>394670</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>395032</t>
+          <t>444394</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5102,32 +5102,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>372090</t>
+          <t>418450</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>349290</t>
+          <t>394670</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>395032</t>
+          <t>444394</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,21%</t>
         </is>
       </c>
     </row>
@@ -5145,17 +5145,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>734393</t>
+          <t>819688</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>734393</t>
+          <t>819688</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>734393</t>
+          <t>819688</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5180,17 +5180,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>734393</t>
+          <t>819688</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>734393</t>
+          <t>819688</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>734393</t>
+          <t>819688</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5227,32 +5227,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>505167</t>
+          <t>297580</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>399490</t>
+          <t>276511</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>624443</t>
+          <t>319156</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5262,32 +5262,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>505167</t>
+          <t>297580</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>399490</t>
+          <t>276511</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>624443</t>
+          <t>319156</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>55,88%</t>
         </is>
       </c>
     </row>
@@ -5305,32 +5305,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>224318</t>
+          <t>273616</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105042</t>
+          <t>252040</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>329995</t>
+          <t>294685</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5340,32 +5340,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>224318</t>
+          <t>273616</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>105042</t>
+          <t>252040</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329995</t>
+          <t>294685</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>51,59%</t>
         </is>
       </c>
     </row>
@@ -5383,17 +5383,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>729485</t>
+          <t>571196</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>729485</t>
+          <t>571196</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>729485</t>
+          <t>571196</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5418,17 +5418,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>729485</t>
+          <t>571196</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>729485</t>
+          <t>571196</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>729485</t>
+          <t>571196</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5465,32 +5465,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>444437</t>
+          <t>478434</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>332508</t>
+          <t>450047</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>493374</t>
+          <t>505885</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5500,32 +5500,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>444437</t>
+          <t>478434</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>332508</t>
+          <t>450047</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>493374</t>
+          <t>505885</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>58,89%</t>
         </is>
       </c>
     </row>
@@ -5543,32 +5543,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>412175</t>
+          <t>380610</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>363238</t>
+          <t>353159</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>524104</t>
+          <t>408997</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5578,32 +5578,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>412175</t>
+          <t>380610</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>363238</t>
+          <t>353159</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>524104</t>
+          <t>408997</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>47,61%</t>
         </is>
       </c>
     </row>
@@ -5621,17 +5621,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>856612</t>
+          <t>859044</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>856612</t>
+          <t>859044</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>856612</t>
+          <t>859044</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5656,17 +5656,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>856612</t>
+          <t>859044</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>856612</t>
+          <t>859044</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>856612</t>
+          <t>859044</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5703,32 +5703,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1583137</t>
+          <t>1466492</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1445705</t>
+          <t>1418108</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1873457</t>
+          <t>1510341</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5738,32 +5738,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1583137</t>
+          <t>1466492</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1445705</t>
+          <t>1418108</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1873457</t>
+          <t>1510341</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -5781,32 +5781,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1247819</t>
+          <t>1336394</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>957499</t>
+          <t>1292545</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1385251</t>
+          <t>1384778</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5816,32 +5816,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1247819</t>
+          <t>1336394</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>957499</t>
+          <t>1292545</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1385251</t>
+          <t>1384778</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,41%</t>
         </is>
       </c>
     </row>
@@ -5859,17 +5859,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5894,17 +5894,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2830956</t>
+          <t>2802886</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
